--- a/fixtures/clean_model.xlsx
+++ b/fixtures/clean_model.xlsx
@@ -615,8 +615,8 @@
         <v>21</v>
       </c>
       <c r="C3">
-        <f>Inputs!B2*0.1</f>
-        <v>100</v>
+        <f>Inputs!B2*Inputs!B3</f>
+        <v>30</v>
       </c>
       <c r="D3">
         <f>C3+1</f>

--- a/fixtures/clean_model.xlsx
+++ b/fixtures/clean_model.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="23" uniqueCount="22">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="24" uniqueCount="23">
   <si>
     <t>Input</t>
   </si>
@@ -44,6 +44,9 @@
   </si>
   <si>
     <t>Inflated</t>
+  </si>
+  <si>
+    <t>Multiplier</t>
   </si>
   <si>
     <t>Rent</t>
@@ -464,10 +467,10 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C6"/>
+  <dimension ref="A1:D6"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:3">
+    <row r="1" spans="1:4">
       <c r="A1" t="s">
         <v>6</v>
       </c>
@@ -477,64 +480,70 @@
       <c r="C1" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="2" spans="1:3">
+      <c r="D1" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4">
       <c r="A2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B2">
         <v>100</v>
       </c>
       <c r="C2">
-        <f>B2*$C$2</f>
+        <f>B2*$D$2</f>
         <v>110.00000000000001</v>
       </c>
-    </row>
-    <row r="3" spans="1:3">
+      <c r="D2">
+        <v>1.1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4">
       <c r="A3" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B3">
         <v>120</v>
       </c>
       <c r="C3">
-        <f>B3*$C$2</f>
+        <f>B3*$D$2</f>
         <v>132.0</v>
       </c>
     </row>
-    <row r="4" spans="1:3">
+    <row r="4" spans="1:4">
       <c r="A4" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B4">
         <v>130</v>
       </c>
       <c r="C4">
-        <f>B4*$C$2</f>
+        <f>B4*$D$2</f>
         <v>143.0</v>
       </c>
     </row>
-    <row r="5" spans="1:3">
+    <row r="5" spans="1:4">
       <c r="A5" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B5">
         <v>140</v>
       </c>
       <c r="C5">
-        <f>B5*$C$2</f>
+        <f>B5*$D$2</f>
         <v>154.0</v>
       </c>
     </row>
-    <row r="6" spans="1:3">
+    <row r="6" spans="1:4">
       <c r="A6" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B6">
         <v>150</v>
       </c>
       <c r="C6">
-        <f>B6*$C$2</f>
+        <f>B6*$D$2</f>
         <v>165.0</v>
       </c>
     </row>
@@ -550,7 +559,7 @@
   <sheetData>
     <row r="1" spans="1:2">
       <c r="A1" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B1" t="s">
         <v>1</v>
@@ -558,7 +567,7 @@
     </row>
     <row r="2" spans="1:2">
       <c r="A2" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B2">
         <f>Inputs!B2*(1+Inputs!B3)</f>
@@ -567,7 +576,7 @@
     </row>
     <row r="3" spans="1:2">
       <c r="A3" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B3">
         <f>SUM(Opex!C2:C6)</f>
@@ -576,7 +585,7 @@
     </row>
     <row r="4" spans="1:2">
       <c r="A4" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B4">
         <f>B2-B3</f>
@@ -585,7 +594,7 @@
     </row>
     <row r="5" spans="1:2">
       <c r="A5" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B5">
         <f>Inputs!B5</f>
@@ -604,15 +613,15 @@
   <sheetData>
     <row r="1" spans="1:4">
       <c r="A1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="3" spans="1:4">
       <c r="A3" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B3" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C3">
         <f>Inputs!B2*Inputs!B3</f>

--- a/fixtures/clean_model.xlsx
+++ b/fixtures/clean_model.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="24" uniqueCount="23">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="28" uniqueCount="23">
   <si>
     <t>Input</t>
   </si>
@@ -130,6 +130,19 @@
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
 </styleSheet>
+</file>
+
+<file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="OpexTable" displayName="OpexTable" ref="A1:D6" totalsRowShown="0">
+  <autoFilter ref="A1:D6"/>
+  <tableColumns count="4">
+    <tableColumn id="1" name="Item"/>
+    <tableColumn id="2" name="Amount"/>
+    <tableColumn id="3" name="Inflated"/>
+    <tableColumn id="4" name="Multiplier"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleMedium9" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -549,6 +562,9 @@
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <tableParts count="1">
+    <tablePart r:id="rId1"/>
+  </tableParts>
 </worksheet>
 </file>
 

--- a/fixtures/clean_model.xlsx
+++ b/fixtures/clean_model.xlsx
@@ -596,7 +596,7 @@
       </c>
       <c r="B3">
         <f>SUM(Opex!C2:C6)</f>
-        <v>660</v>
+        <v>704</v>
       </c>
     </row>
     <row r="4" spans="1:2">
@@ -605,7 +605,7 @@
       </c>
       <c r="B4">
         <f>B2-B3</f>
-        <v>370</v>
+        <v>326</v>
       </c>
     </row>
     <row r="5" spans="1:2">
